--- a/artfynd/A 68643-2021 artfynd.xlsx
+++ b/artfynd/A 68643-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68643-2021 artfynd.xlsx
+++ b/artfynd/A 68643-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97363344</v>
+        <v>102283350</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Furusjön, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524036.4977830972</v>
+        <v>524236</v>
       </c>
       <c r="R2" t="n">
-        <v>7028508.654677478</v>
+        <v>7027759</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,40 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97363331</v>
+        <v>102284261</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523828.9140112625</v>
+        <v>524112</v>
       </c>
       <c r="R3" t="n">
-        <v>7028103.038147273</v>
+        <v>7027652</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,40 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97363330</v>
+        <v>102283349</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523869.4903636598</v>
+        <v>524055</v>
       </c>
       <c r="R4" t="n">
-        <v>7028202.4553487</v>
+        <v>7028145</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,40 +950,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Gammal björk</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97363352</v>
+        <v>102284257</v>
       </c>
       <c r="B5" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Furusjön, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524062.4946247436</v>
+        <v>524130</v>
       </c>
       <c r="R5" t="n">
-        <v>7028574.769212909</v>
+        <v>7027438</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,40 +1047,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Kolad tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97363329</v>
+        <v>102284258</v>
       </c>
       <c r="B6" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523879.2179331384</v>
+        <v>523920</v>
       </c>
       <c r="R6" t="n">
-        <v>7027981.869114774</v>
+        <v>7027976</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,40 +1144,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102283333</v>
+        <v>102284259</v>
       </c>
       <c r="B7" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524027.2161980578</v>
+        <v>523948</v>
       </c>
       <c r="R7" t="n">
-        <v>7028129.634640927</v>
+        <v>7028391</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1353,19 +1228,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102284262</v>
+        <v>102282236</v>
       </c>
       <c r="B8" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524015.7596583972</v>
+        <v>524027</v>
       </c>
       <c r="R8" t="n">
-        <v>7027920.546325698</v>
+        <v>7028354</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,19 +1325,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102284223</v>
+        <v>102282237</v>
       </c>
       <c r="B9" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524001.6402874903</v>
+        <v>524112</v>
       </c>
       <c r="R9" t="n">
-        <v>7028426.328558028</v>
+        <v>7028582</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,19 +1422,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,27 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102283340</v>
+        <v>102284225</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524151.4630366098</v>
+        <v>524087</v>
       </c>
       <c r="R10" t="n">
-        <v>7027792.390632535</v>
+        <v>7027874</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1689,19 +1519,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102284261</v>
+        <v>102283333</v>
       </c>
       <c r="B11" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524112.0988548415</v>
+        <v>524027</v>
       </c>
       <c r="R11" t="n">
-        <v>7027651.699402856</v>
+        <v>7028129</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1801,19 +1616,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102284251</v>
+        <v>102284260</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524094.1721895364</v>
+        <v>523808</v>
       </c>
       <c r="R12" t="n">
-        <v>7027825.599325499</v>
+        <v>7027997</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,19 +1713,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,53 +1742,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102284225</v>
+        <v>97363331</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524087.5170971583</v>
+        <v>523829</v>
       </c>
       <c r="R13" t="n">
-        <v>7027874.438801652</v>
+        <v>7028103</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2022,22 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,69 +1823,73 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102283349</v>
+        <v>97363344</v>
       </c>
       <c r="B14" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stor-Furusjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524054.9440528793</v>
+        <v>524037</v>
       </c>
       <c r="R14" t="n">
-        <v>7028145.091282535</v>
+        <v>7028508</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,22 +1913,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,35 +1929,39 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102282264</v>
+        <v>102282262</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2216,10 +1989,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523825.5425375233</v>
+        <v>524027</v>
       </c>
       <c r="R15" t="n">
-        <v>7028194.055600056</v>
+        <v>7027742</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,19 +2022,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,19 +2051,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102284252</v>
+        <v>102282263</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2324,17 +2082,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524022.8847195641</v>
+        <v>524042</v>
       </c>
       <c r="R16" t="n">
-        <v>7027928.673046403</v>
+        <v>7027838</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2361,19 +2119,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,65 +2136,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102284237</v>
+        <v>102282264</v>
       </c>
       <c r="B17" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523792.5362435071</v>
+        <v>523826</v>
       </c>
       <c r="R17" t="n">
-        <v>7028042.669343157</v>
+        <v>7028194</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2473,19 +2216,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,49 +2233,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102282250</v>
+        <v>102282265</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2280,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524026.4360277997</v>
+        <v>524114</v>
       </c>
       <c r="R18" t="n">
-        <v>7028353.41674016</v>
+        <v>7028594</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2585,19 +2313,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,19 +2342,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102284247</v>
+        <v>102283348</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2664,10 +2377,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524060.2676603761</v>
+        <v>524009</v>
       </c>
       <c r="R19" t="n">
-        <v>7028452.778185747</v>
+        <v>7028084</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2697,19 +2410,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,37 +2439,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102283335</v>
+        <v>102284243</v>
       </c>
       <c r="B20" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2776,10 +2474,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524128.7867711039</v>
+        <v>524130</v>
       </c>
       <c r="R20" t="n">
-        <v>7028238.93040105</v>
+        <v>7027441</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2809,19 +2507,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,19 +2536,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102282262</v>
+        <v>102284244</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2884,17 +2567,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524026.981721107</v>
+        <v>523863</v>
       </c>
       <c r="R21" t="n">
-        <v>7027741.666937555</v>
+        <v>7028117</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2921,19 +2604,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,49 +2621,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102284264</v>
+        <v>102284246</v>
       </c>
       <c r="B22" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3000,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524001.6402874903</v>
+        <v>523802</v>
       </c>
       <c r="R22" t="n">
-        <v>7028426.328558028</v>
+        <v>7028303</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3033,19 +2701,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3072,19 +2730,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102284249</v>
+        <v>102284247</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3112,10 +2765,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524124.2154239235</v>
+        <v>524060</v>
       </c>
       <c r="R23" t="n">
-        <v>7027653.13626547</v>
+        <v>7028453</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3145,19 +2798,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3184,53 +2827,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102282236</v>
+        <v>102284249</v>
       </c>
       <c r="B24" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524026.4360277997</v>
+        <v>524124</v>
       </c>
       <c r="R24" t="n">
-        <v>7028353.41674016</v>
+        <v>7027653</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3257,19 +2895,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,49 +2912,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102283342</v>
+        <v>102284250</v>
       </c>
       <c r="B25" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3336,10 +2959,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524192.1240189204</v>
+        <v>524127</v>
       </c>
       <c r="R25" t="n">
-        <v>7027760.851163482</v>
+        <v>7027675</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3369,19 +2992,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,37 +3021,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>102284258</v>
+        <v>102284251</v>
       </c>
       <c r="B26" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3448,10 +3056,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523920.1287109889</v>
+        <v>524094</v>
       </c>
       <c r="R26" t="n">
-        <v>7027976.34366463</v>
+        <v>7027825</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3481,19 +3089,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,37 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>102284221</v>
+        <v>102284252</v>
       </c>
       <c r="B27" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3560,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523804.981347346</v>
+        <v>524023</v>
       </c>
       <c r="R27" t="n">
-        <v>7027999.705491002</v>
+        <v>7027929</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3593,19 +3186,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3632,19 +3215,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102284250</v>
+        <v>102284253</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3672,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524127.1938993055</v>
+        <v>523805</v>
       </c>
       <c r="R28" t="n">
-        <v>7027675.137820575</v>
+        <v>7028180</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3705,19 +3283,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3744,37 +3312,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>102284222</v>
+        <v>102284254</v>
       </c>
       <c r="B29" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3784,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524006.4550760834</v>
+        <v>523810</v>
       </c>
       <c r="R29" t="n">
-        <v>7027963.533999634</v>
+        <v>7028237</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3817,19 +3380,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3856,37 +3409,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102284231</v>
+        <v>102284255</v>
       </c>
       <c r="B30" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524010.5641341642</v>
+        <v>523837</v>
       </c>
       <c r="R30" t="n">
-        <v>7027954.594545372</v>
+        <v>7028392</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3929,19 +3477,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3968,15 +3506,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>102284255</v>
+        <v>97363329</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3984,37 +3517,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523837.0904200021</v>
+        <v>523880</v>
       </c>
       <c r="R31" t="n">
-        <v>7028392.363110439</v>
+        <v>7027982</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4038,22 +3571,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,31 +3587,35 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>102284254</v>
+        <v>97363352</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4096,37 +3623,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stor-Furusjön, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523809.9545035373</v>
+        <v>524063</v>
       </c>
       <c r="R32" t="n">
-        <v>7028236.993405345</v>
+        <v>7028575</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4150,22 +3677,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4176,31 +3693,35 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Kolad tallhögstubbe</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>102284219</v>
+        <v>102284265</v>
       </c>
       <c r="B33" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4208,21 +3729,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4232,10 +3753,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524123.3846830259</v>
+        <v>524015</v>
       </c>
       <c r="R33" t="n">
-        <v>7027644.158894667</v>
+        <v>7027921</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4265,19 +3786,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4304,15 +3815,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>102284244</v>
+        <v>102284218</v>
       </c>
       <c r="B34" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,21 +3826,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4344,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523862.487648257</v>
+        <v>523790</v>
       </c>
       <c r="R34" t="n">
-        <v>7028117.639736607</v>
+        <v>7028313</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4377,19 +3883,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4416,53 +3912,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>102284227</v>
+        <v>102282253</v>
       </c>
       <c r="B35" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524086.1117622704</v>
+        <v>524014</v>
       </c>
       <c r="R35" t="n">
-        <v>7027822.399005241</v>
+        <v>7028475</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4489,19 +3980,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4516,27 +3997,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>102282263</v>
+        <v>102282254</v>
       </c>
       <c r="B36" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4544,21 +4020,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4568,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524041.9808925779</v>
+        <v>524053</v>
       </c>
       <c r="R36" t="n">
-        <v>7027837.766134295</v>
+        <v>7028455</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4601,19 +4077,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4633,22 +4099,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>102282254</v>
+        <v>102282255</v>
       </c>
       <c r="B37" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4680,10 +4141,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524053.0664297566</v>
+        <v>524102</v>
       </c>
       <c r="R37" t="n">
-        <v>7028454.966322499</v>
+        <v>7028573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4713,19 +4174,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4745,22 +4196,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>102284238</v>
+        <v>102283344</v>
       </c>
       <c r="B38" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,10 +4238,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524013.0239828697</v>
+        <v>524115</v>
       </c>
       <c r="R38" t="n">
-        <v>7028405.336792395</v>
+        <v>7028246</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4825,19 +4271,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4864,15 +4300,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>102283715</v>
+        <v>102284236</v>
       </c>
       <c r="B39" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4880,42 +4311,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524151.8828413826</v>
+        <v>523814</v>
       </c>
       <c r="R39" t="n">
-        <v>7028392.03025317</v>
+        <v>7027981</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4945,19 +4368,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4977,22 +4390,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Eva Karlsson, Benny Öwre</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>102284259</v>
+        <v>102284237</v>
       </c>
       <c r="B40" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,21 +4408,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5024,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523948.0217057267</v>
+        <v>523793</v>
       </c>
       <c r="R40" t="n">
-        <v>7028390.499766625</v>
+        <v>7028043</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5057,19 +4465,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5096,15 +4494,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>102282239</v>
+        <v>102284238</v>
       </c>
       <c r="B41" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5112,37 +4505,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524183.1957446726</v>
+        <v>524013</v>
       </c>
       <c r="R41" t="n">
-        <v>7027753.607114132</v>
+        <v>7028405</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5169,19 +4562,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,65 +4579,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>102282231</v>
+        <v>102284239</v>
       </c>
       <c r="B42" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6450</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524080.1542379439</v>
+        <v>524108</v>
       </c>
       <c r="R42" t="n">
-        <v>7028555.171095934</v>
+        <v>7027712</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5281,19 +4659,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5308,27 +4676,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>102284236</v>
+        <v>102282231</v>
       </c>
       <c r="B43" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,37 +4699,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6450</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523814.1031145487</v>
+        <v>524080</v>
       </c>
       <c r="R43" t="n">
-        <v>7027980.93596659</v>
+        <v>7028555</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5393,19 +4756,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5420,65 +4773,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>102284240</v>
+        <v>102282222</v>
       </c>
       <c r="B44" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523813.1878888148</v>
+        <v>524038</v>
       </c>
       <c r="R44" t="n">
-        <v>7028224.908644806</v>
+        <v>7027834</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5505,19 +4853,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5532,49 +4870,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>102284232</v>
+        <v>102283335</v>
       </c>
       <c r="B45" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5584,10 +4917,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523806.5420156456</v>
+        <v>524129</v>
       </c>
       <c r="R45" t="n">
-        <v>7028212.750413718</v>
+        <v>7028239</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5617,19 +4950,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5656,15 +4979,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>102284253</v>
+        <v>102284219</v>
       </c>
       <c r="B46" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,21 +4990,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5696,10 +5014,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523804.5399703455</v>
+        <v>524123</v>
       </c>
       <c r="R46" t="n">
-        <v>7028179.996597298</v>
+        <v>7027644</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5729,19 +5047,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5768,15 +5076,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>102283348</v>
+        <v>102284221</v>
       </c>
       <c r="B47" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5784,21 +5087,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5808,10 +5111,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524008.6913261762</v>
+        <v>523805</v>
       </c>
       <c r="R47" t="n">
-        <v>7028084.646607541</v>
+        <v>7028000</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5841,19 +5144,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5880,15 +5173,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>102282238</v>
+        <v>102284222</v>
       </c>
       <c r="B48" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,37 +5184,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524138.4555284505</v>
+        <v>524006</v>
       </c>
       <c r="R48" t="n">
-        <v>7027790.049936021</v>
+        <v>7027963</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5953,19 +5241,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,27 +5258,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>102282222</v>
+        <v>102284223</v>
       </c>
       <c r="B49" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6028,17 +5301,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524037.9691768912</v>
+        <v>524001</v>
       </c>
       <c r="R49" t="n">
-        <v>7027833.699269689</v>
+        <v>7028426</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6065,19 +5338,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6092,49 +5355,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>102284246</v>
+        <v>102284227</v>
       </c>
       <c r="B50" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6144,10 +5402,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523802.279836692</v>
+        <v>524086</v>
       </c>
       <c r="R50" t="n">
-        <v>7028302.861224101</v>
+        <v>7027823</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6177,19 +5435,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6216,15 +5464,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>102283341</v>
+        <v>97363330</v>
       </c>
       <c r="B51" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6252,17 +5495,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524096.7878603905</v>
+        <v>523869</v>
       </c>
       <c r="R51" t="n">
-        <v>7028552.605604392</v>
+        <v>7028202</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6286,22 +5529,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6312,69 +5545,73 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Gammal björk</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>102284260</v>
+        <v>102282238</v>
       </c>
       <c r="B52" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523808.1449600927</v>
+        <v>524139</v>
       </c>
       <c r="R52" t="n">
-        <v>7027997.037960216</v>
+        <v>7027790</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6401,19 +5638,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6428,27 +5655,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>102284235</v>
+        <v>102282239</v>
       </c>
       <c r="B53" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6476,17 +5698,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524087.5170971583</v>
+        <v>524183</v>
       </c>
       <c r="R53" t="n">
-        <v>7027874.438801652</v>
+        <v>7027754</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6513,19 +5735,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6540,27 +5752,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>102282251</v>
+        <v>102282249</v>
       </c>
       <c r="B54" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6592,10 +5799,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524104.6979651137</v>
+        <v>523880</v>
       </c>
       <c r="R54" t="n">
-        <v>7028575.534946728</v>
+        <v>7028202</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6625,19 +5832,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6657,22 +5854,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102284265</v>
+        <v>102282250</v>
       </c>
       <c r="B55" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6680,37 +5872,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524014.8614597772</v>
+        <v>524027</v>
       </c>
       <c r="R55" t="n">
-        <v>7027920.539593427</v>
+        <v>7028354</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6737,19 +5929,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6764,27 +5946,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>102282249</v>
+        <v>102282251</v>
       </c>
       <c r="B56" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6816,10 +5993,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523879.3763634813</v>
+        <v>524105</v>
       </c>
       <c r="R56" t="n">
-        <v>7028201.632064704</v>
+        <v>7028575</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6849,19 +6026,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6881,60 +6048,55 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>102282227</v>
+        <v>102283340</v>
       </c>
       <c r="B57" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524087.062588034</v>
+        <v>524152</v>
       </c>
       <c r="R57" t="n">
-        <v>7027994.63763026</v>
+        <v>7027792</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6961,19 +6123,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6988,27 +6140,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102282255</v>
+        <v>102283341</v>
       </c>
       <c r="B58" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7016,37 +6163,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524101.5785292926</v>
+        <v>524097</v>
       </c>
       <c r="R58" t="n">
-        <v>7028572.372487755</v>
+        <v>7028552</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7073,19 +6220,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7100,27 +6237,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>102282237</v>
+        <v>102283342</v>
       </c>
       <c r="B59" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7128,37 +6260,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524111.3892001266</v>
+        <v>524192</v>
       </c>
       <c r="R59" t="n">
-        <v>7028581.414844208</v>
+        <v>7027761</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7185,19 +6317,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7212,49 +6334,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>102284224</v>
+        <v>102283343</v>
       </c>
       <c r="B60" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7264,10 +6381,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524074.2840984999</v>
+        <v>524239</v>
       </c>
       <c r="R60" t="n">
-        <v>7027902.147728136</v>
+        <v>7027767</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7297,19 +6414,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7336,15 +6443,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102283344</v>
+        <v>102284235</v>
       </c>
       <c r="B61" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,21 +6454,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7376,10 +6478,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524114.8154407843</v>
+        <v>524087</v>
       </c>
       <c r="R61" t="n">
-        <v>7028245.552298695</v>
+        <v>7027874</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7409,19 +6511,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7448,53 +6540,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102282253</v>
+        <v>102283337</v>
       </c>
       <c r="B62" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524013.853397071</v>
+        <v>524240</v>
       </c>
       <c r="R62" t="n">
-        <v>7028474.40355957</v>
+        <v>7027770</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7521,19 +6608,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7548,49 +6625,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102284239</v>
+        <v>102284224</v>
       </c>
       <c r="B63" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7600,10 +6672,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524108.5026994013</v>
+        <v>524074</v>
       </c>
       <c r="R63" t="n">
-        <v>7027711.77820303</v>
+        <v>7027902</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7633,19 +6705,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7669,6 +6731,790 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>102284241</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>524130</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7027441</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>102284262</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>524016</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7027921</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>102284264</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>524001</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7028426</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>102283715</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>524152</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7028392</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Maria Danvind, Johan Råghall, Eva Karlsson, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>102284240</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>523813</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7028225</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>102284231</v>
+      </c>
+      <c r="B69" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>524011</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7027954</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>102284232</v>
+      </c>
+      <c r="B70" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>523806</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7028213</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>102282227</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Norbergsknulen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>524087</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7027994</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 68643-2021 artfynd.xlsx
+++ b/artfynd/A 68643-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283350</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284261</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283349</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284257</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284258</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284259</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282236</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282237</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284225</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283333</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284260</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363331</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363344</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2048,6 +2118,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282262</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2145,6 +2220,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282263</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2242,6 +2322,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282264</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2339,6 +2424,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282265</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283348</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2533,6 +2628,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284243</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2630,6 +2730,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284244</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2727,6 +2832,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284246</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2824,6 +2934,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284247</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2921,6 +3036,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284249</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3018,6 +3138,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284250</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3115,6 +3240,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284251</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3212,6 +3342,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284252</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3309,6 +3444,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284253</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3406,6 +3546,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284254</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3503,6 +3648,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284255</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3609,6 +3759,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363329</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3715,6 +3870,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363352</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3812,6 +3972,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284265</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3909,6 +4074,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284218</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4006,6 +4176,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282253</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4103,6 +4278,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282254</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4200,6 +4380,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282255</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4297,6 +4482,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283344</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4394,6 +4584,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284236</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4491,6 +4686,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284237</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4588,6 +4788,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284238</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4685,6 +4890,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284239</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4782,6 +4992,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282231</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4879,6 +5094,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282222</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4976,6 +5196,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283335</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5073,6 +5298,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284219</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5170,6 +5400,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284221</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5267,6 +5502,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284222</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5364,6 +5604,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284223</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5461,6 +5706,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284227</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5567,6 +5817,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363330</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5664,6 +5919,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282238</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5761,6 +6021,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282239</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5858,6 +6123,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282249</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5955,6 +6225,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282250</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6052,6 +6327,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282251</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6149,6 +6429,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283340</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6246,6 +6531,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283341</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6343,6 +6633,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283342</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6440,6 +6735,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283343</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6537,6 +6837,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284235</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6634,6 +6939,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283337</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6731,6 +7041,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284224</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6828,6 +7143,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284241</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6925,6 +7245,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284262</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7022,6 +7347,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284264</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7127,6 +7457,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283715</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7224,6 +7559,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284240</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7321,6 +7661,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284231</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7418,6 +7763,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284232</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7515,8 +7865,85 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282227</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>